--- a/data/modelling/clustering/tv/df_alt_to_client_clust.xlsx
+++ b/data/modelling/clustering/tv/df_alt_to_client_clust.xlsx
@@ -906,7 +906,7 @@
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3219,7 @@
       <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6374,7 @@
       <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6491,7 @@
       <c r="AL44" t="inlineStr"/>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -6981,7 +6981,7 @@
       <c r="AL48" t="inlineStr"/>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7751,7 @@
       <c r="AL54" t="inlineStr"/>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7993,7 @@
       <c r="AL56" t="inlineStr"/>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       <c r="AL57" t="inlineStr"/>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -8656,7 +8656,7 @@
       <c r="AL61" t="inlineStr"/>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -9537,7 +9537,7 @@
       <c r="AL68" t="inlineStr"/>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -9843,7 +9843,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       <c r="AL83" t="inlineStr"/>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -11738,7 +11738,7 @@
       <c r="AL85" t="inlineStr"/>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -12944,7 +12944,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -13440,7 +13440,7 @@
       <c r="AL97" t="inlineStr"/>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -13774,7 +13774,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -14697,7 +14697,7 @@
       <c r="AL106" t="inlineStr"/>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -14854,7 +14854,7 @@
       <c r="AL107" t="inlineStr"/>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15126,7 @@
       <c r="AL109" t="inlineStr"/>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -15846,7 +15846,7 @@
       <c r="AL115" t="inlineStr"/>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16485,7 @@
       <c r="AL120" t="inlineStr"/>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -17726,7 +17726,7 @@
       <c r="AL129" t="inlineStr"/>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17978,7 @@
       <c r="AL131" t="inlineStr"/>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -18127,7 +18127,7 @@
       <c r="AL132" t="inlineStr"/>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -19196,7 +19196,7 @@
       <c r="AL141" t="inlineStr"/>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -19317,7 +19317,7 @@
       <c r="AL142" t="inlineStr"/>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -20059,7 +20059,7 @@
       <c r="AL148" t="inlineStr"/>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -20341,7 +20341,7 @@
       <c r="AL150" t="inlineStr"/>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -20788,7 +20788,7 @@
       <c r="AL153" t="inlineStr"/>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -20879,7 +20879,7 @@
       <c r="AL154" t="inlineStr"/>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -21002,7 +21002,7 @@
       <c r="AL155" t="inlineStr"/>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -21915,7 +21915,7 @@
       <c r="AL162" t="inlineStr"/>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -22705,7 +22705,7 @@
       <c r="AL168" t="inlineStr"/>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -22858,7 +22858,7 @@
       <c r="AL169" t="inlineStr"/>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -22951,7 +22951,7 @@
       <c r="AL170" t="inlineStr"/>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -26226,7 +26226,7 @@
       <c r="AL195" t="inlineStr"/>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -26577,7 +26577,7 @@
       <c r="AL198" t="inlineStr"/>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -27571,7 +27571,7 @@
       <c r="AL206" t="inlineStr"/>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -27658,7 +27658,7 @@
       <c r="AL207" t="inlineStr"/>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -28085,7 +28085,7 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -29269,7 +29269,7 @@
       <c r="AL220" t="inlineStr"/>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -29481,7 +29481,7 @@
       <c r="AL222" t="inlineStr"/>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -31815,7 +31815,7 @@
       <c r="AL242" t="inlineStr"/>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -32638,7 +32638,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -33842,7 +33842,7 @@
       <c r="AL259" t="inlineStr"/>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -33983,7 +33983,7 @@
       </c>
       <c r="AM260" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -35128,7 +35128,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -35767,7 +35767,7 @@
       </c>
       <c r="AM274" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -36456,7 +36456,7 @@
       <c r="AL279" t="inlineStr"/>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -36740,7 +36740,7 @@
       <c r="AL281" t="inlineStr"/>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -38585,7 +38585,7 @@
       <c r="AL296" t="inlineStr"/>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -39489,7 +39489,7 @@
       <c r="AL304" t="inlineStr"/>
       <c r="AM304" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -39976,7 +39976,7 @@
       <c r="AL309" t="inlineStr"/>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -40365,7 +40365,7 @@
       <c r="AL312" t="inlineStr"/>
       <c r="AM312" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -41776,7 +41776,7 @@
       <c r="AL325" t="inlineStr"/>
       <c r="AM325" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -42095,7 +42095,7 @@
       <c r="AL328" t="inlineStr"/>
       <c r="AM328" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -42882,7 +42882,7 @@
       <c r="AL335" t="inlineStr"/>
       <c r="AM335" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -43213,7 +43213,7 @@
       <c r="AL338" t="inlineStr"/>
       <c r="AM338" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -43985,7 +43985,7 @@
       <c r="AL346" t="inlineStr"/>
       <c r="AM346" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -45666,7 +45666,7 @@
       <c r="AL361" t="inlineStr"/>
       <c r="AM361" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
@@ -45985,7 +45985,7 @@
       <c r="AL364" t="inlineStr"/>
       <c r="AM364" t="inlineStr">
         <is>
-          <t>Barato pero calidad madia/baja</t>
+          <t>Barato pero calidad media/baja</t>
         </is>
       </c>
     </row>
